--- a/Backend/中医诊断学/八纲证候判断表.xlsx
+++ b/Backend/中医诊断学/八纲证候判断表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\12968\Desktop\naoji\-app\Backend\中医诊断学\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C69B1C-6E3A-4155-BCE0-E131343FE6AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98D3CBA-6A05-417F-8B16-2F43B54B7E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3098" yWindow="2340" windowWidth="18000" windowHeight="10433" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="新建 文本文档 (3)" sheetId="4" r:id="rId1"/>
@@ -56,169 +56,172 @@
     <t>病位</t>
   </si>
   <si>
+    <t>表证</t>
+  </si>
+  <si>
+    <t>exterior syndrome/pattern</t>
+  </si>
+  <si>
+    <t>六淫疫疠邪气经皮毛、口鼻侵入所致。多见于外感病初期，起病急、病程短。[1]</t>
+  </si>
+  <si>
+    <t>皮毛、肌腠、经络（外）。[2]</t>
+  </si>
+  <si>
+    <t>**恶寒与发热同时并见**；**脉浮**；**舌苔通常无明显变化（薄白）**；头身疼痛。[1, 3]</t>
+  </si>
+  <si>
+    <t>兼见鼻塞、流涕、咳嗽、喷嚏、咽喉痒痛等。[1]</t>
+  </si>
+  <si>
+    <t>里证</t>
+  </si>
+  <si>
+    <t>interior syndrome/pattern</t>
+  </si>
+  <si>
+    <t>**但热不寒**或**但寒不热**；**脉沉**；**舌苔常有质与色的显著变化（如厚、腻、黄、焦等）**。[3, 4]</t>
+  </si>
+  <si>
+    <t>半表半里证</t>
+  </si>
+  <si>
+    <t>half-exterior and half-interior syndrome/pattern</t>
+  </si>
+  <si>
+    <t>半表半里（枢机不利）。[5]</t>
+  </si>
+  <si>
+    <t>默默不欲饮食、心烦喜呕。[5]</t>
+  </si>
+  <si>
+    <t>寒证</t>
+  </si>
+  <si>
+    <t>cold syndrome/pattern</t>
+  </si>
+  <si>
+    <t>热证</t>
+  </si>
+  <si>
+    <t>heat syndrome/pattern</t>
+  </si>
+  <si>
+    <t>1.表邪内传入里；2.外邪直接侵犯脏腑；3.七情、饮食、劳逸损伤脏腑。[1]</t>
+  </si>
+  <si>
+    <t>脏腑、气血、骨髓（内）。[2]</t>
+  </si>
+  <si>
+    <t>或见壮热恶热、烦躁神昏；或见畏寒肢冷、倦卧神疲、大便溏泄、小便清长。[4]</t>
+  </si>
+  <si>
+    <t>外邪由表内传尚未入里，或里邪透表尚未达表，邪正相搏于表里之间。[5]</t>
+  </si>
+  <si>
+    <t>**寒热往来（恶寒与发热交替发作，界限分明）**；**脉弦**；胸胁苦满；口苦咽干目眩。[5]</t>
+  </si>
+  <si>
+    <t>感受寒邪，或机体自身阳虚阴盛所致。[3]</t>
+  </si>
+  <si>
+    <t>全身或局部[6]</t>
+  </si>
+  <si>
+    <t>**恶寒喜暖**；**口淡不渴**；**分泌物及排泄物（痰、涎、涕、尿）清稀色白**；**舌淡苔白润滑**；**脉迟或紧**。[6]</t>
+  </si>
+  <si>
+    <t>面色㿠白、肢冷蜷卧、大便稀溏、小便清长。[3]</t>
+  </si>
+  <si>
+    <t>感受热邪，或机体自身阴虚阳亢所致。[6]</t>
+  </si>
+  <si>
+    <t>**恶热喜冷**；**口渴喜冷饮**；**分泌物及排泄物（痰、涕、粪）黄稠臭秽**；**舌红苔黄而干燥**；**脉数**。[6, 7]</t>
+  </si>
+  <si>
+    <t>面红目赤、烦躁不宁、吐血衄血、大便干结、小便短赤。[6]</t>
+  </si>
+  <si>
+    <t>虚证</t>
+  </si>
+  <si>
+    <t>deficiency syndrome/pattern</t>
+  </si>
+  <si>
+    <t>先天不足、后天失养或由于疾病耗损导致正气虚弱。[8]</t>
+  </si>
+  <si>
+    <t>全身或脏腑[8]</t>
+  </si>
+  <si>
+    <t>面色淡白或萎黄、精神萎靡、身疲乏力、自汗、大便滑脱、小便失禁。[8]</t>
+  </si>
+  <si>
+    <t>实证</t>
+  </si>
+  <si>
+    <t>excess syndrome/pattern</t>
+  </si>
+  <si>
+    <t>外邪侵入，或体内痰饮、水湿、瘀血等病理产物停积。[10]</t>
+  </si>
+  <si>
+    <t>全身或局部[10]</t>
+  </si>
+  <si>
+    <t>**声高息粗**；**脉象有力**；**腹痛拒按（胀满痛剧）**；**暴病多实**；**舌质苍老、苔厚腻**。[9, 10]</t>
+  </si>
+  <si>
+    <t>发热、烦躁、神昏谵语、呼吸气粗、痰涎壅盛、大便秘结、小便不利。[10]</t>
+  </si>
+  <si>
+    <t>阴证</t>
+  </si>
+  <si>
+    <t>yin syndrome/pattern</t>
+  </si>
+  <si>
+    <t>里、寒、虚证的综合归纳。由阳气虚衰或寒邪凝滞引起。[11]</t>
+  </si>
+  <si>
+    <t>脏腑气血[11]</t>
+  </si>
+  <si>
+    <t>**面色暗淡**；**身重蜷卧**；**语声低怯**；**口淡不渴**；**脉沉迟、微细或弱**。[12]</t>
+  </si>
+  <si>
+    <t>精神萎靡、形寒肢冷、倦怠无力、大便稀溏、小便清长、舌淡胖嫩。[12]</t>
+  </si>
+  <si>
+    <t>阳证</t>
+  </si>
+  <si>
+    <t>yang syndrome/pattern</t>
+  </si>
+  <si>
+    <t>表、热、实证的综合归纳。由阳气亢盛、火热内炽引起。[12]</t>
+  </si>
+  <si>
+    <t>体表或脏腑[12]</t>
+  </si>
+  <si>
+    <t>**面色红赤**；**语声壮厉（烦而多言）**；**口干烦渴引饮**；**腹痛拒按**；**脉浮洪、数大、滑实有力**。[12, 13]</t>
+  </si>
+  <si>
+    <t>发热、肌肤灼热、躁动不安、呼吸气粗、大便秘结、舌质红绛。[12]</t>
+  </si>
+  <si>
     <t>核心临床表现（含判断关键）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>可能/伴见表现</t>
-  </si>
-  <si>
-    <t>表证</t>
-  </si>
-  <si>
-    <t>exterior syndrome/pattern</t>
-  </si>
-  <si>
-    <t>六淫疫疠邪气经皮毛、口鼻侵入所致。多见于外感病初期，起病急、病程短。[1]</t>
-  </si>
-  <si>
-    <t>皮毛、肌腠、经络（外）。[2]</t>
-  </si>
-  <si>
-    <t>**恶寒与发热同时并见**；**脉浮**；**舌苔通常无明显变化（薄白）**；头身疼痛。[1, 3]</t>
-  </si>
-  <si>
-    <t>兼见鼻塞、流涕、咳嗽、喷嚏、咽喉痒痛等。[1]</t>
-  </si>
-  <si>
-    <t>里证</t>
-  </si>
-  <si>
-    <t>interior syndrome/pattern</t>
-  </si>
-  <si>
-    <t>**但热不寒**或**但寒不热**；**脉沉**；**舌苔常有质与色的显著变化（如厚、腻、黄、焦等）**。[3, 4]</t>
-  </si>
-  <si>
-    <t>半表半里证</t>
-  </si>
-  <si>
-    <t>half-exterior and half-interior syndrome/pattern</t>
-  </si>
-  <si>
-    <t>半表半里（枢机不利）。[5]</t>
-  </si>
-  <si>
-    <t>默默不欲饮食、心烦喜呕。[5]</t>
-  </si>
-  <si>
-    <t>寒证</t>
-  </si>
-  <si>
-    <t>cold syndrome/pattern</t>
-  </si>
-  <si>
-    <t>热证</t>
-  </si>
-  <si>
-    <t>heat syndrome/pattern</t>
-  </si>
-  <si>
-    <t>1.表邪内传入里；2.外邪直接侵犯脏腑；3.七情、饮食、劳逸损伤脏腑。[1]</t>
-  </si>
-  <si>
-    <t>脏腑、气血、骨髓（内）。[2]</t>
-  </si>
-  <si>
-    <t>或见壮热恶热、烦躁神昏；或见畏寒肢冷、倦卧神疲、大便溏泄、小便清长。[4]</t>
-  </si>
-  <si>
-    <t>外邪由表内传尚未入里，或里邪透表尚未达表，邪正相搏于表里之间。[5]</t>
-  </si>
-  <si>
-    <t>**寒热往来（恶寒与发热交替发作，界限分明）**；**脉弦**；胸胁苦满；口苦咽干目眩。[5]</t>
-  </si>
-  <si>
-    <t>感受寒邪，或机体自身阳虚阴盛所致。[3]</t>
-  </si>
-  <si>
-    <t>全身或局部[6]</t>
-  </si>
-  <si>
-    <t>**恶寒喜暖**；**口淡不渴**；**分泌物及排泄物（痰、涎、涕、尿）清稀色白**；**舌淡苔白润滑**；**脉迟或紧**。[6]</t>
-  </si>
-  <si>
-    <t>面色㿠白、肢冷蜷卧、大便稀溏、小便清长。[3]</t>
-  </si>
-  <si>
-    <t>感受热邪，或机体自身阴虚阳亢所致。[6]</t>
-  </si>
-  <si>
-    <t>**恶热喜冷**；**口渴喜冷饮**；**分泌物及排泄物（痰、涕、粪）黄稠臭秽**；**舌红苔黄而干燥**；**脉数**。[6, 7]</t>
-  </si>
-  <si>
-    <t>面红目赤、烦躁不宁、吐血衄血、大便干结、小便短赤。[6]</t>
-  </si>
-  <si>
-    <t>虚证</t>
-  </si>
-  <si>
-    <t>deficiency syndrome/pattern</t>
-  </si>
-  <si>
-    <t>先天不足、后天失养或由于疾病耗损导致正气虚弱。[8]</t>
-  </si>
-  <si>
-    <t>全身或脏腑[8]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>**声息低微**；**脉象无力（按之空虚）**；**久病多虚**；**舌质淡嫩、少苔**。[8, 9]</t>
-  </si>
-  <si>
-    <t>面色淡白或萎黄、精神萎靡、身疲乏力、自汗、大便滑脱、小便失禁。[8]</t>
-  </si>
-  <si>
-    <t>实证</t>
-  </si>
-  <si>
-    <t>excess syndrome/pattern</t>
-  </si>
-  <si>
-    <t>外邪侵入，或体内痰饮、水湿、瘀血等病理产物停积。[10]</t>
-  </si>
-  <si>
-    <t>全身或局部[10]</t>
-  </si>
-  <si>
-    <t>**声高息粗**；**脉象有力**；**腹痛拒按（胀满痛剧）**；**暴病多实**；**舌质苍老、苔厚腻**。[9, 10]</t>
-  </si>
-  <si>
-    <t>发热、烦躁、神昏谵语、呼吸气粗、痰涎壅盛、大便秘结、小便不利。[10]</t>
-  </si>
-  <si>
-    <t>阴证</t>
-  </si>
-  <si>
-    <t>yin syndrome/pattern</t>
-  </si>
-  <si>
-    <t>里、寒、虚证的综合归纳。由阳气虚衰或寒邪凝滞引起。[11]</t>
-  </si>
-  <si>
-    <t>脏腑气血[11]</t>
-  </si>
-  <si>
-    <t>**面色暗淡**；**身重蜷卧**；**语声低怯**；**口淡不渴**；**脉沉迟、微细或弱**。[12]</t>
-  </si>
-  <si>
-    <t>精神萎靡、形寒肢冷、倦怠无力、大便稀溏、小便清长、舌淡胖嫩。[12]</t>
-  </si>
-  <si>
-    <t>阳证</t>
-  </si>
-  <si>
-    <t>yang syndrome/pattern</t>
-  </si>
-  <si>
-    <t>表、热、实证的综合归纳。由阳气亢盛、火热内炽引起。[12]</t>
-  </si>
-  <si>
-    <t>体表或脏腑[12]</t>
-  </si>
-  <si>
-    <t>**面色红赤**；**语声壮厉（烦而多言）**；**口干烦渴引饮**；**腹痛拒按**；**脉浮洪、数大、滑实有力**。[12, 13]</t>
-  </si>
-  <si>
-    <t>发热、肌肤灼热、躁动不安、呼吸气粗、大便秘结、舌质红绛。[12]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -599,7 +602,7 @@
     <col min="2" max="2" width="43.265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="72.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="72.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="93.33203125" customWidth="1"/>
     <col min="6" max="6" width="72.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -617,190 +620,190 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
         <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
         <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
         <v>35</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>36</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" t="s">
         <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
         <v>41</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E8" t="s">
         <v>42</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" t="s">
         <v>43</v>
-      </c>
-      <c r="D8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
         <v>47</v>
       </c>
-      <c r="B9" t="s">
+      <c r="E9" t="s">
         <v>48</v>
       </c>
-      <c r="C9" t="s">
+      <c r="F9" t="s">
         <v>49</v>
-      </c>
-      <c r="D9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
         <v>53</v>
       </c>
-      <c r="B10" t="s">
+      <c r="E10" t="s">
         <v>54</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="s">
         <v>55</v>
-      </c>
-      <c r="D10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
